--- a/samsung/dist/20261030_三星電子個股模型_v0.4.xlsx
+++ b/samsung/dist/20261030_三星電子個股模型_v0.4.xlsx
@@ -5157,7 +5157,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">v0.4</t>
+      <t xml:space="preserve">v0.3.3</t>
     </r>
     <r>
       <rPr>
@@ -5387,7 +5387,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">v0.4</t>
+      <t xml:space="preserve">v0.3.3</t>
     </r>
     <r>
       <rPr>
@@ -5890,6 +5890,9 @@
     <t xml:space="preserve">%</t>
   </si>
   <si>
+    <t xml:space="preserve">Interested-party</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -6173,9 +6176,6 @@
       </rPr>
       <t xml:space="preserve">位元季增</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Interested-party</t>
   </si>
   <si>
     <r>
@@ -33921,7 +33921,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">結構（法說 </t>
+      <t xml:space="preserve">結構 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Assumed]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（法說 </t>
     </r>
     <r>
       <rPr>
@@ -33959,7 +33978,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">、位元低至中個位數；</t>
+      <t xml:space="preserve">、位元低至中個位數，</t>
     </r>
     <r>
       <rPr>
@@ -33997,26 +34016,83 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">、位元中個位數，兩者營收增幅相近）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[Derived]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；淨利 </t>
+      <t xml:space="preserve">、位元中個位數，兩者營收增幅相近；但價量相乘約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，高於記憶體營收實際季增 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，差距可能來自韓元升值的匯率影響〔法說：季減約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">兆，以零組件為主〕與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ASP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">口徑）；淨利 </t>
     </r>
     <r>
       <rPr>
@@ -44630,65 +44706,94 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">vs DS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業利益（公司）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三星 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-29 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">確定財報：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DS 106.5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">兆；差額＝晶圓代工與 </t>
+      <t xml:space="preserve">vs Meritz </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">估計</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Meritz Securities 2026-10-08</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Herald Business </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Interested-party]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；本模型＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DS 106.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋晶圓代工與 </t>
     </r>
     <r>
       <rPr>
@@ -44717,7 +44822,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">[Derived]</t>
+      <t xml:space="preserve">1.5</t>
     </r>
   </si>
   <si>
@@ -46820,18 +46925,18 @@
         <v>0.07</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>51</v>
@@ -46849,15 +46954,15 @@
         <v>41</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>51</v>
@@ -46872,18 +46977,18 @@
         <v>0.09</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>51</v>
@@ -46901,15 +47006,15 @@
         <v>41</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>51</v>
@@ -46924,7 +47029,7 @@
         <v>0.19</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>65</v>
@@ -46950,7 +47055,7 @@
         <v>0.15</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>68</v>
@@ -46976,7 +47081,7 @@
         <v>0.18</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>71</v>
@@ -47002,7 +47107,7 @@
         <v>0.2</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>74</v>
@@ -47309,7 +47414,7 @@
         <v>0.22</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>110</v>
@@ -47335,7 +47440,7 @@
         <v>0.33</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>113</v>
@@ -47361,7 +47466,7 @@
         <v>0.41</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>116</v>
@@ -48221,7 +48326,7 @@
         <v>1</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H74" s="8" t="s">
         <v>228</v>
@@ -48241,7 +48346,7 @@
         <v>1.4</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H75" s="8" t="s">
         <v>231</v>
@@ -48261,7 +48366,7 @@
         <v>2</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H76" s="8" t="s">
         <v>234</v>
@@ -48340,7 +48445,7 @@
         <v>-0.025</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H81" s="8" t="s">
         <v>245</v>
@@ -48360,7 +48465,7 @@
         <v>0.125</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H82" s="4" t="s">
         <v>215</v>
@@ -48380,7 +48485,7 @@
         <v>0.475</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>215</v>
@@ -48400,7 +48505,7 @@
         <v>0.95</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H84" s="4" t="s">
         <v>215</v>
@@ -48420,7 +48525,7 @@
         <v>0.605</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H85" s="4" t="s">
         <v>215</v>
@@ -48440,7 +48545,7 @@
         <v>0.155</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H86" s="4" t="s">
         <v>215</v>
@@ -48460,7 +48565,7 @@
         <v>0.125</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H87" s="4" t="s">
         <v>215</v>
@@ -49320,7 +49425,7 @@
         <v>0</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H124" s="8" t="s">
         <v>336</v>
@@ -49340,7 +49445,7 @@
         <v>0.05</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>215</v>
@@ -49360,7 +49465,7 @@
         <v>0.3</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H126" s="4" t="s">
         <v>215</v>
@@ -49380,7 +49485,7 @@
         <v>0.875</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H127" s="4" t="s">
         <v>215</v>
@@ -49400,7 +49505,7 @@
         <v>0.725</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H128" s="4" t="s">
         <v>215</v>
@@ -49420,7 +49525,7 @@
         <v>0.15</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H129" s="4" t="s">
         <v>215</v>
@@ -49440,7 +49545,7 @@
         <v>0.175</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H130" s="4" t="s">
         <v>215</v>
@@ -50305,7 +50410,7 @@
         <v>5.4</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H168" s="4" t="s">
         <v>428</v>
@@ -50325,7 +50430,7 @@
         <v>2.4</v>
       </c>
       <c r="G169" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H169" s="4" t="s">
         <v>215</v>
@@ -50345,7 +50450,7 @@
         <v>0.5</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H170" s="4" t="s">
         <v>215</v>
@@ -50365,7 +50470,7 @@
         <v>260</v>
       </c>
       <c r="G171" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H171" s="4" t="s">
         <v>215</v>
@@ -50385,7 +50490,7 @@
         <v>280</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H172" s="4" t="s">
         <v>215</v>
@@ -50405,7 +50510,7 @@
         <v>288</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H173" s="4" t="s">
         <v>215</v>
@@ -50425,7 +50530,7 @@
         <v>1.7</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H174" s="8" t="s">
         <v>442</v>
@@ -50445,7 +50550,7 @@
         <v>7</v>
       </c>
       <c r="G175" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H175" s="4" t="s">
         <v>215</v>
@@ -50465,7 +50570,7 @@
         <v>7</v>
       </c>
       <c r="G176" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H176" s="4" t="s">
         <v>215</v>
@@ -50485,7 +50590,7 @@
         <v>288</v>
       </c>
       <c r="G177" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H177" s="4" t="s">
         <v>215</v>
@@ -50505,7 +50610,7 @@
         <v>288</v>
       </c>
       <c r="G178" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H178" s="4" t="s">
         <v>215</v>
@@ -50525,7 +50630,7 @@
         <v>288</v>
       </c>
       <c r="G179" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H179" s="4" t="s">
         <v>215</v>
@@ -50623,7 +50728,7 @@
         <v>1024</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H183" s="8" t="s">
         <v>462</v>
@@ -50643,7 +50748,7 @@
         <v>1024</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H184" s="4" t="s">
         <v>215</v>
@@ -50663,7 +50768,7 @@
         <v>1024</v>
       </c>
       <c r="G185" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H185" s="4" t="s">
         <v>215</v>
@@ -50683,7 +50788,7 @@
         <v>0.5</v>
       </c>
       <c r="G186" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H186" s="8" t="s">
         <v>469</v>
@@ -50703,7 +50808,7 @@
         <v>0</v>
       </c>
       <c r="G187" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H187" s="4" t="s">
         <v>215</v>
@@ -50723,7 +50828,7 @@
         <v>0</v>
       </c>
       <c r="G188" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H188" s="4" t="s">
         <v>215</v>
@@ -50743,7 +50848,7 @@
         <v>141</v>
       </c>
       <c r="G189" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H189" s="4" t="s">
         <v>215</v>
@@ -50763,7 +50868,7 @@
         <v>141</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H190" s="4" t="s">
         <v>215</v>
@@ -50783,7 +50888,7 @@
         <v>141</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H191" s="4" t="s">
         <v>215</v>
@@ -50959,7 +51064,7 @@
         <v>3.85</v>
       </c>
       <c r="G198" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H198" s="8" t="s">
         <v>496</v>
@@ -50979,7 +51084,7 @@
         <v>5.5</v>
       </c>
       <c r="G199" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H199" s="4" t="s">
         <v>215</v>
@@ -50999,7 +51104,7 @@
         <v>7</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H200" s="4" t="s">
         <v>215</v>
@@ -51019,7 +51124,7 @@
         <v>192</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H201" s="4" t="s">
         <v>215</v>
@@ -51039,7 +51144,7 @@
         <v>250</v>
       </c>
       <c r="G202" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H202" s="4" t="s">
         <v>215</v>
@@ -51059,7 +51164,7 @@
         <v>288</v>
       </c>
       <c r="G203" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H203" s="4" t="s">
         <v>215</v>
@@ -51577,7 +51682,7 @@
         <v>0.8</v>
       </c>
       <c r="G225" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H225" s="8" t="s">
         <v>554</v>
@@ -51629,7 +51734,7 @@
         <v>0.63</v>
       </c>
       <c r="G227" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H227" s="8" t="s">
         <v>560</v>
@@ -51681,7 +51786,7 @@
         <v>16</v>
       </c>
       <c r="G229" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H229" s="8" t="s">
         <v>567</v>
@@ -51707,7 +51812,7 @@
         <v>1.21</v>
       </c>
       <c r="G230" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H230" s="8" t="s">
         <v>570</v>
@@ -51733,7 +51838,7 @@
         <v>0.25</v>
       </c>
       <c r="G231" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H231" s="8" t="s">
         <v>573</v>
@@ -52018,7 +52123,7 @@
         <v>54.6</v>
       </c>
       <c r="G243" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H243" s="8" t="s">
         <v>608</v>
@@ -52038,7 +52143,7 @@
         <v>77.4</v>
       </c>
       <c r="G244" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H244" s="8" t="s">
         <v>611</v>
@@ -52058,7 +52163,7 @@
         <v>152.8</v>
       </c>
       <c r="G245" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H245" s="8" t="s">
         <v>614</v>
@@ -52449,7 +52554,7 @@
         <v>725000</v>
       </c>
       <c r="G263" s="9" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H263" s="9" t="s">
         <v>660</v>
@@ -52471,7 +52576,7 @@
       </c>
       <c r="F264" s="9"/>
       <c r="G264" s="9" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H264" s="9" t="s">
         <v>663</v>
@@ -52493,7 +52598,7 @@
       </c>
       <c r="F265" s="9"/>
       <c r="G265" s="9" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H265" s="9" t="s">
         <v>663</v>
@@ -52515,7 +52620,7 @@
       </c>
       <c r="F266" s="9"/>
       <c r="G266" s="9" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H266" s="9" t="s">
         <v>663</v>
@@ -60234,7 +60339,7 @@
         <v>1039</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60254,7 +60359,7 @@
         <v>1042</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60274,7 +60379,7 @@
         <v>1046</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60294,7 +60399,7 @@
         <v>1039</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62001,13 +62106,13 @@
         <v>108</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>106.5</v>
+        <v>111.9</v>
       </c>
       <c r="D10" s="15" t="n">
         <f aca="false">B10/C10-1</f>
-        <v>0.0140845070422535</v>
-      </c>
-      <c r="E10" s="4" t="s">
+        <v>-0.0348525469168901</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>1182</v>
       </c>
     </row>
